--- a/shop/dist/05-Small-Business-12-Month-Cash-Flow-Forecast.xlsx
+++ b/shop/dist/05-Small-Business-12-Month-Cash-Flow-Forecast.xlsx
@@ -286,7 +286,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Cash Flow'!A22</f>
+              <f>'Cash Flow'!A23</f>
             </strRef>
           </tx>
           <spPr>
@@ -304,7 +304,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Cash Flow'!$B$22:$M$22</f>
+              <f>'Cash Flow'!$B$23:$M$23</f>
             </numRef>
           </val>
         </ser>
@@ -389,7 +389,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Cash Flow'!A19</f>
+              <f>'Cash Flow'!A20</f>
             </strRef>
           </tx>
           <spPr>
@@ -399,7 +399,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Cash Flow'!$B$19:$M$19</f>
+              <f>'Cash Flow'!$B$20:$M$20</f>
             </numRef>
           </val>
         </ser>
@@ -841,7 +841,7 @@
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>•  Cash Flow — timing-aware collections, supplier terms, HST remittance and tax instalments.</t>
+          <t>•  Cash Flow — timing-aware collections, supplier terms, HST remitted net of input tax credits, tax instalments.</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2.  Set your collection terms — how much you get paid in month, and how much 30 days later.</t>
+          <t>2.  Set your collection terms, and enter anything customers already owe you as opening receivables.</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1145,22 +1145,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Opening accounts receivable (collected in month 1)</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Share of costs that carry HST (for input tax credits)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Collection percentages should add to 100%. Supplier terms should add to 100%.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="20">
+    <row r="22">
+      <c r="B22" s="20">
         <f>IF(ROUND(B8+B9+B10,4)=1,"Collections OK","⚠ Collections do not add to 100%")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="20">
+    <row r="23">
+      <c r="B23" s="20">
         <f>IF(ROUND(B11+B12,4)=1,"Supplier terms OK","⚠ Supplier terms do not add to 100%")</f>
         <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Opening accounts receivable is what customers already owe you on day one. It lands in month 1 collections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Input tax credits: HST you pay on purchases is claimed back, so the model remits sales tax NET, not gross.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +2935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3031,47 +3065,47 @@
         <v/>
       </c>
       <c r="C5" s="23">
-        <f>B22</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="D5" s="23">
-        <f>C22</f>
+        <f>C23</f>
         <v/>
       </c>
       <c r="E5" s="23">
-        <f>D22</f>
+        <f>D23</f>
         <v/>
       </c>
       <c r="F5" s="23">
-        <f>E22</f>
+        <f>E23</f>
         <v/>
       </c>
       <c r="G5" s="23">
-        <f>F22</f>
+        <f>F23</f>
         <v/>
       </c>
       <c r="H5" s="23">
-        <f>G22</f>
+        <f>G23</f>
         <v/>
       </c>
       <c r="I5" s="23">
-        <f>H22</f>
+        <f>H23</f>
         <v/>
       </c>
       <c r="J5" s="23">
-        <f>I22</f>
+        <f>I23</f>
         <v/>
       </c>
       <c r="K5" s="23">
-        <f>J22</f>
+        <f>J23</f>
         <v/>
       </c>
       <c r="L5" s="23">
-        <f>K22</f>
+        <f>K23</f>
         <v/>
       </c>
       <c r="M5" s="23">
-        <f>L22</f>
+        <f>L23</f>
         <v/>
       </c>
     </row>
@@ -3102,7 +3136,7 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>Revenue!B9*Assumptions!$B$8</f>
+        <f>Revenue!B9*Assumptions!$B$8+Assumptions!$B$19</f>
         <v/>
       </c>
       <c r="C8" s="22">
@@ -3472,55 +3506,55 @@
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>Sales tax remitted</t>
+          <t>Sales tax paid on purchases</t>
         </is>
       </c>
       <c r="B16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(1,3)=0,SUM(B9:B9),0),B9))</f>
+        <f>(Costs!B5+Costs!B22+Costs!B25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="C16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(2,3)=0,SUM(B9:C9),0),C9))</f>
+        <f>(Costs!C5+Costs!C22+Costs!C25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="D16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(3,3)=0,SUM(B9:D9),0),D9))</f>
+        <f>(Costs!D5+Costs!D22+Costs!D25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="E16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(4,3)=0,SUM(C9:E9),0),E9))</f>
+        <f>(Costs!E5+Costs!E22+Costs!E25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="F16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(5,3)=0,SUM(D9:F9),0),F9))</f>
+        <f>(Costs!F5+Costs!F22+Costs!F25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="G16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(6,3)=0,SUM(E9:G9),0),G9))</f>
+        <f>(Costs!G5+Costs!G22+Costs!G25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="H16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(7,3)=0,SUM(F9:H9),0),H9))</f>
+        <f>(Costs!H5+Costs!H22+Costs!H25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="I16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(8,3)=0,SUM(G9:I9),0),I9))</f>
+        <f>(Costs!I5+Costs!I22+Costs!I25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="J16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(9,3)=0,SUM(H9:J9),0),J9))</f>
+        <f>(Costs!J5+Costs!J22+Costs!J25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="K16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(10,3)=0,SUM(I9:K9),0),K9))</f>
+        <f>(Costs!K5+Costs!K22+Costs!K25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="L16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(11,3)=0,SUM(J9:L9),0),L9))</f>
+        <f>(Costs!L5+Costs!L22+Costs!L25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="M16" s="22">
-        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(12,3)=0,SUM(K9:M9),0),M9))</f>
+        <f>(Costs!M5+Costs!M22+Costs!M25)*Assumptions!$B$20*Assumptions!$B$14</f>
         <v/>
       </c>
       <c r="N16" s="22">
@@ -3531,55 +3565,55 @@
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>Equipment, loan repayments &amp; draws</t>
+          <t>Sales tax remitted (net of input tax credits)</t>
         </is>
       </c>
       <c r="B17" s="22">
-        <f>Costs!B25+Costs!B27+Costs!B28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(1,3)=0,SUM(B9:B9)-SUM(B16:B16),0),B9-B16))</f>
         <v/>
       </c>
       <c r="C17" s="22">
-        <f>Costs!C25+Costs!C27+Costs!C28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(2,3)=0,SUM(B9:C9)-SUM(B16:C16),0),C9-C16))</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>Costs!D25+Costs!D27+Costs!D28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(3,3)=0,SUM(B9:D9)-SUM(B16:D16),0),D9-D16))</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>Costs!E25+Costs!E27+Costs!E28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(4,3)=0,SUM(C9:E9)-SUM(C16:E16),0),E9-E16))</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>Costs!F25+Costs!F27+Costs!F28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(5,3)=0,SUM(D9:F9)-SUM(D16:F16),0),F9-F16))</f>
         <v/>
       </c>
       <c r="G17" s="22">
-        <f>Costs!G25+Costs!G27+Costs!G28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(6,3)=0,SUM(E9:G9)-SUM(E16:G16),0),G9-G16))</f>
         <v/>
       </c>
       <c r="H17" s="22">
-        <f>Costs!H25+Costs!H27+Costs!H28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(7,3)=0,SUM(F9:H9)-SUM(F16:H16),0),H9-H16))</f>
         <v/>
       </c>
       <c r="I17" s="22">
-        <f>Costs!I25+Costs!I27+Costs!I28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(8,3)=0,SUM(G9:I9)-SUM(G16:I16),0),I9-I16))</f>
         <v/>
       </c>
       <c r="J17" s="22">
-        <f>Costs!J25+Costs!J27+Costs!J28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(9,3)=0,SUM(H9:J9)-SUM(H16:J16),0),J9-J16))</f>
         <v/>
       </c>
       <c r="K17" s="22">
-        <f>Costs!K25+Costs!K27+Costs!K28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(10,3)=0,SUM(I9:K9)-SUM(I16:K16),0),K9-K16))</f>
         <v/>
       </c>
       <c r="L17" s="22">
-        <f>Costs!L25+Costs!L27+Costs!L28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(11,3)=0,SUM(J9:L9)-SUM(J16:L16),0),L9-L16))</f>
         <v/>
       </c>
       <c r="M17" s="22">
-        <f>Costs!M25+Costs!M27+Costs!M28</f>
+        <f>IF(Assumptions!$B$14=0,0,IF(Assumptions!$B$15="Yes",IF(MOD(12,3)=0,SUM(K9:M9)-SUM(K16:M16),0),M9-M16))</f>
         <v/>
       </c>
       <c r="N17" s="22">
@@ -3590,55 +3624,55 @@
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>Income tax instalment</t>
+          <t>Equipment, loan repayments &amp; draws</t>
         </is>
       </c>
       <c r="B18" s="22">
-        <f>MAX(0,(Revenue!B9-Costs!B5-Costs!B22))*Assumptions!$B$16</f>
+        <f>Costs!B25+Costs!B27+Costs!B28</f>
         <v/>
       </c>
       <c r="C18" s="22">
-        <f>MAX(0,(Revenue!C9-Costs!C5-Costs!C22))*Assumptions!$B$16</f>
+        <f>Costs!C25+Costs!C27+Costs!C28</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>MAX(0,(Revenue!D9-Costs!D5-Costs!D22))*Assumptions!$B$16</f>
+        <f>Costs!D25+Costs!D27+Costs!D28</f>
         <v/>
       </c>
       <c r="E18" s="22">
-        <f>MAX(0,(Revenue!E9-Costs!E5-Costs!E22))*Assumptions!$B$16</f>
+        <f>Costs!E25+Costs!E27+Costs!E28</f>
         <v/>
       </c>
       <c r="F18" s="22">
-        <f>MAX(0,(Revenue!F9-Costs!F5-Costs!F22))*Assumptions!$B$16</f>
+        <f>Costs!F25+Costs!F27+Costs!F28</f>
         <v/>
       </c>
       <c r="G18" s="22">
-        <f>MAX(0,(Revenue!G9-Costs!G5-Costs!G22))*Assumptions!$B$16</f>
+        <f>Costs!G25+Costs!G27+Costs!G28</f>
         <v/>
       </c>
       <c r="H18" s="22">
-        <f>MAX(0,(Revenue!H9-Costs!H5-Costs!H22))*Assumptions!$B$16</f>
+        <f>Costs!H25+Costs!H27+Costs!H28</f>
         <v/>
       </c>
       <c r="I18" s="22">
-        <f>MAX(0,(Revenue!I9-Costs!I5-Costs!I22))*Assumptions!$B$16</f>
+        <f>Costs!I25+Costs!I27+Costs!I28</f>
         <v/>
       </c>
       <c r="J18" s="22">
-        <f>MAX(0,(Revenue!J9-Costs!J5-Costs!J22))*Assumptions!$B$16</f>
+        <f>Costs!J25+Costs!J27+Costs!J28</f>
         <v/>
       </c>
       <c r="K18" s="22">
-        <f>MAX(0,(Revenue!K9-Costs!K5-Costs!K22))*Assumptions!$B$16</f>
+        <f>Costs!K25+Costs!K27+Costs!K28</f>
         <v/>
       </c>
       <c r="L18" s="22">
-        <f>MAX(0,(Revenue!L9-Costs!L5-Costs!L22))*Assumptions!$B$16</f>
+        <f>Costs!L25+Costs!L27+Costs!L28</f>
         <v/>
       </c>
       <c r="M18" s="22">
-        <f>MAX(0,(Revenue!M9-Costs!M5-Costs!M22))*Assumptions!$B$16</f>
+        <f>Costs!M25+Costs!M27+Costs!M28</f>
         <v/>
       </c>
       <c r="N18" s="22">
@@ -3647,175 +3681,175 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Income tax instalment</t>
+        </is>
+      </c>
+      <c r="B19" s="22">
+        <f>MAX(0,(Revenue!B9-Costs!B5-Costs!B22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="C19" s="22">
+        <f>MAX(0,(Revenue!C9-Costs!C5-Costs!C22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
+        <f>MAX(0,(Revenue!D9-Costs!D5-Costs!D22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="E19" s="22">
+        <f>MAX(0,(Revenue!E9-Costs!E5-Costs!E22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>MAX(0,(Revenue!F9-Costs!F5-Costs!F22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="G19" s="22">
+        <f>MAX(0,(Revenue!G9-Costs!G5-Costs!G22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="H19" s="22">
+        <f>MAX(0,(Revenue!H9-Costs!H5-Costs!H22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="I19" s="22">
+        <f>MAX(0,(Revenue!I9-Costs!I5-Costs!I22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="J19" s="22">
+        <f>MAX(0,(Revenue!J9-Costs!J5-Costs!J22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="K19" s="22">
+        <f>MAX(0,(Revenue!K9-Costs!K5-Costs!K22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>MAX(0,(Revenue!L9-Costs!L5-Costs!L22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="M19" s="22">
+        <f>MAX(0,(Revenue!M9-Costs!M5-Costs!M22))*Assumptions!$B$16</f>
+        <v/>
+      </c>
+      <c r="N19" s="22">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>TOTAL CASH OUT</t>
         </is>
       </c>
-      <c r="B19" s="23">
-        <f>B14+B15+B16+B17+B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="23">
-        <f>C14+C15+C16+C17+C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="23">
-        <f>D14+D15+D16+D17+D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
-        <f>E14+E15+E16+E17+E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="23">
-        <f>F14+F15+F16+F17+F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="23">
-        <f>G14+G15+G16+G17+G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="23">
-        <f>H14+H15+H16+H17+H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="23">
-        <f>I14+I15+I16+I17+I18</f>
-        <v/>
-      </c>
-      <c r="J19" s="23">
-        <f>J14+J15+J16+J17+J18</f>
-        <v/>
-      </c>
-      <c r="K19" s="23">
-        <f>K14+K15+K16+K17+K18</f>
-        <v/>
-      </c>
-      <c r="L19" s="23">
-        <f>L14+L15+L16+L17+L18</f>
-        <v/>
-      </c>
-      <c r="M19" s="23">
-        <f>M14+M15+M16+M17+M18</f>
-        <v/>
-      </c>
-      <c r="N19" s="23">
-        <f>SUM(B19:M19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>NET CASH MOVEMENT</t>
-        </is>
-      </c>
-      <c r="B21" s="23">
-        <f>B11-B19</f>
-        <v/>
-      </c>
-      <c r="C21" s="23">
-        <f>C11-C19</f>
-        <v/>
-      </c>
-      <c r="D21" s="23">
-        <f>D11-D19</f>
-        <v/>
-      </c>
-      <c r="E21" s="23">
-        <f>E11-E19</f>
-        <v/>
-      </c>
-      <c r="F21" s="23">
-        <f>F11-F19</f>
-        <v/>
-      </c>
-      <c r="G21" s="23">
-        <f>G11-G19</f>
-        <v/>
-      </c>
-      <c r="H21" s="23">
-        <f>H11-H19</f>
-        <v/>
-      </c>
-      <c r="I21" s="23">
-        <f>I11-I19</f>
-        <v/>
-      </c>
-      <c r="J21" s="23">
-        <f>J11-J19</f>
-        <v/>
-      </c>
-      <c r="K21" s="23">
-        <f>K11-K19</f>
-        <v/>
-      </c>
-      <c r="L21" s="23">
-        <f>L11-L19</f>
-        <v/>
-      </c>
-      <c r="M21" s="23">
-        <f>M11-M19</f>
-        <v/>
-      </c>
-      <c r="N21" s="23">
-        <f>SUM(B21:M21)</f>
+      <c r="B20" s="23">
+        <f>B14+B15+B16+B17+B18+B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="23">
+        <f>C14+C15+C16+C17+C18+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="23">
+        <f>D14+D15+D16+D17+D18+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="23">
+        <f>E14+E15+E16+E17+E18+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="23">
+        <f>F14+F15+F16+F17+F18+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
+        <f>G14+G15+G16+G17+G18+G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="23">
+        <f>H14+H15+H16+H17+H18+H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="23">
+        <f>I14+I15+I16+I17+I18+I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="23">
+        <f>J14+J15+J16+J17+J18+J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="23">
+        <f>K14+K15+K16+K17+K18+K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="23">
+        <f>L14+L15+L16+L17+L18+L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="23">
+        <f>M14+M15+M16+M17+M18+M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="23">
+        <f>SUM(B20:M20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>CLOSING CASH</t>
+          <t>NET CASH MOVEMENT</t>
         </is>
       </c>
       <c r="B22" s="23">
-        <f>B5+B21</f>
+        <f>B11-B20</f>
         <v/>
       </c>
       <c r="C22" s="23">
-        <f>C5+C21</f>
+        <f>C11-C20</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>D5+D21</f>
+        <f>D11-D20</f>
         <v/>
       </c>
       <c r="E22" s="23">
-        <f>E5+E21</f>
+        <f>E11-E20</f>
         <v/>
       </c>
       <c r="F22" s="23">
-        <f>F5+F21</f>
+        <f>F11-F20</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f>G5+G21</f>
+        <f>G11-G20</f>
         <v/>
       </c>
       <c r="H22" s="23">
-        <f>H5+H21</f>
+        <f>H11-H20</f>
         <v/>
       </c>
       <c r="I22" s="23">
-        <f>I5+I21</f>
+        <f>I11-I20</f>
         <v/>
       </c>
       <c r="J22" s="23">
-        <f>J5+J21</f>
+        <f>J11-J20</f>
         <v/>
       </c>
       <c r="K22" s="23">
-        <f>K5+K21</f>
+        <f>K11-K20</f>
         <v/>
       </c>
       <c r="L22" s="23">
-        <f>L5+L21</f>
+        <f>L11-L20</f>
         <v/>
       </c>
       <c r="M22" s="23">
-        <f>M5+M21</f>
+        <f>M11-M20</f>
         <v/>
       </c>
       <c r="N22" s="23">
@@ -3823,58 +3857,117 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>CLOSING CASH</t>
+        </is>
+      </c>
+      <c r="B23" s="23">
+        <f>B5+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="23">
+        <f>C5+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>D5+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>E5+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>F5+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="23">
+        <f>G5+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="23">
+        <f>H5+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="23">
+        <f>I5+I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="23">
+        <f>J5+J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="23">
+        <f>K5+K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="23">
+        <f>L5+L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="23">
+        <f>M5+M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="23">
+        <f>SUM(B23:M23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Cash warning</t>
         </is>
       </c>
-      <c r="B24" s="20">
-        <f>IF(B22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="C24" s="20">
-        <f>IF(C22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f>IF(D22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f>IF(E22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>IF(F22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="G24" s="20">
-        <f>IF(G22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="H24" s="20">
-        <f>IF(H22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="I24" s="20">
-        <f>IF(I22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="J24" s="20">
-        <f>IF(J22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="K24" s="20">
-        <f>IF(K22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="L24" s="20">
-        <f>IF(L22&lt;0,"⚠ SHORT","OK")</f>
-        <v/>
-      </c>
-      <c r="M24" s="20">
-        <f>IF(M22&lt;0,"⚠ SHORT","OK")</f>
+      <c r="B25" s="20">
+        <f>IF(B23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>IF(C23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f>IF(D23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="E25" s="20">
+        <f>IF(E23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="F25" s="20">
+        <f>IF(F23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="G25" s="20">
+        <f>IF(G23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="H25" s="20">
+        <f>IF(H23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="I25" s="20">
+        <f>IF(I23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="J25" s="20">
+        <f>IF(J23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="K25" s="20">
+        <f>IF(K23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="L25" s="20">
+        <f>IF(L23&lt;0,"⚠ SHORT","OK")</f>
+        <v/>
+      </c>
+      <c r="M25" s="20">
+        <f>IF(M23&lt;0,"⚠ SHORT","OK")</f>
         <v/>
       </c>
     </row>
@@ -4017,7 +4110,7 @@
         </is>
       </c>
       <c r="B13" s="23">
-        <f>'Cash Flow'!M22</f>
+        <f>'Cash Flow'!M23</f>
         <v/>
       </c>
     </row>
@@ -4028,7 +4121,7 @@
         </is>
       </c>
       <c r="B14" s="23">
-        <f>MIN('Cash Flow'!B22:M22)</f>
+        <f>MIN('Cash Flow'!B23:M23)</f>
         <v/>
       </c>
     </row>
@@ -4039,7 +4132,7 @@
         </is>
       </c>
       <c r="B15" s="29">
-        <f>COUNTIF('Cash Flow'!B22:M22,"&lt;0")</f>
+        <f>COUNTIF('Cash Flow'!B23:M23,"&lt;0")</f>
         <v/>
       </c>
     </row>
